--- a/output/pdf_financials_xlsx/TAU.xlsx
+++ b/output/pdf_financials_xlsx/TAU.xlsx
@@ -5853,10 +5853,10 @@
         <v>0</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>18.150865</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>19.412615</v>
       </c>
     </row>
     <row r="93">
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.077149</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0.01125</v>
@@ -7284,7 +7284,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.314729</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0.075</v>
@@ -7293,28 +7293,28 @@
         <v>0.1025</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.32526</v>
+        <v>-1.478478</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>4.74</v>
+        <v>-0.40472</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-24.763779</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-47.907102</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-22.829708</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-32.816342</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-20.369029</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-29.950752</v>
       </c>
     </row>
     <row r="119">
@@ -10672,7 +10672,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -21488,7 +21492,11 @@
           <t>Exploration and evaluation asset expenditures $</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -25370,7 +25378,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -28838,7 +28850,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -30364,7 +30380,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -31310,7 +31330,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -34132,7 +34156,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E276" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TAU.xlsx
+++ b/output/pdf_financials_xlsx/TAU.xlsx
@@ -1044,25 +1044,25 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.06461600000000001</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.265158</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.14988</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.455698</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>1.148457</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.399589</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>1.139819</v>
       </c>
     </row>
     <row r="13">
@@ -1969,25 +1969,25 @@
         <v>-2.105353</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.847676</v>
+        <v>-3.912292</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-8.054083</v>
+        <v>-8.319241</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-7.460221</v>
+        <v>-7.610101</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.419289</v>
+        <v>-0.036409</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>1.959058</v>
+        <v>0.810601</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.920091</v>
+        <v>0.520502</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.516798</v>
+        <v>-3.656617</v>
       </c>
     </row>
     <row r="28">
@@ -2083,25 +2083,25 @@
         <v>-2.105353</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.847676</v>
+        <v>-3.912292</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-8.054083</v>
+        <v>-8.319241</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-7.460221</v>
+        <v>-7.610101</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.419289</v>
+        <v>-0.036409</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>1.959058</v>
+        <v>0.810601</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>1.014406</v>
+        <v>0.6148169999999999</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.303321</v>
+        <v>-3.44314</v>
       </c>
     </row>
     <row r="30">
@@ -2354,49 +2354,49 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.008508999999999999</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.11791</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.122993</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.021555</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.045006</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.076734</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.050178</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.377498</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>10.171024</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>34.121748</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>31.484044</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>17.198551</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>7.265418</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>9.390294000000001</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>76.105041</v>
       </c>
     </row>
     <row r="35">
@@ -2468,49 +2468,49 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.008508999999999999</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.11791</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.122993</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.021555</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.045006</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.076734</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.050178</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.01</v>
+        <v>0.387498</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.01</v>
+        <v>10.181024</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.01</v>
+        <v>34.131748</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.01</v>
+        <v>31.494044</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.01</v>
+        <v>17.208551</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.010538</v>
+        <v>7.275956</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.035907</v>
+        <v>9.426201000000001</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>76.105041</v>
       </c>
     </row>
     <row r="37">
@@ -3152,49 +3152,49 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.008508999999999999</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.11791</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.122993</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.021555</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.049288</v>
+        <v>0.004282</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.110799</v>
+        <v>0.034065</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.090297</v>
+        <v>0.040119</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.279286</v>
+        <v>0.901788</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>10.402529</v>
+        <v>0.231505</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>36.168636</v>
+        <v>2.046888</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>41.628765</v>
+        <v>10.144721</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>27.578483</v>
+        <v>10.379932</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>13.188809</v>
+        <v>5.923391</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>14.423533</v>
+        <v>5.033239</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>78.598422</v>
+        <v>2.493381</v>
       </c>
     </row>
     <row r="49">
@@ -7653,10 +7653,10 @@
         <v>0</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.143369</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.263859</v>
       </c>
     </row>
     <row r="125">
@@ -7710,10 +7710,10 @@
         <v>0</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.143369</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.263859</v>
       </c>
     </row>
     <row r="126">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11152,7 +11152,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -21782,7 +21782,11 @@
           <t>Return of reclamation deposit</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -22438,7 +22442,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -25664,7 +25672,11 @@
           <t>Purchase of reclamation deposit</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -25754,7 +25766,11 @@
           <t>Return of reclamation deposit (note 14)</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -28758,7 +28774,11 @@
           <t>Purchase of a reclamation deposit</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -36500,7 +36520,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -36592,7 +36612,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -37990,7 +38010,7 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">

--- a/output/pdf_financials_xlsx/TAU.xlsx
+++ b/output/pdf_financials_xlsx/TAU.xlsx
@@ -4348,10 +4348,10 @@
         <v>0</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.8145520000000001</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.722125</v>
       </c>
     </row>
     <row r="68">
@@ -6897,16 +6897,16 @@
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.110852</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.148286</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.329136</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.40321</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
@@ -8242,16 +8242,16 @@
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.110852</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.148286</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.329136</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.40321</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
@@ -8299,16 +8299,16 @@
         <v>-2.429326</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-1.666574</v>
+        <v>-1.777426</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-1.104723</v>
+        <v>-1.253009</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>2.121477</v>
+        <v>1.792341</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-9.890302</v>
+        <v>-10.293512</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>4.475208</v>
@@ -20964,7 +20964,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -24750,7 +24754,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -27104,7 +27112,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -27194,7 +27206,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
